--- a/cadastro.xlsx
+++ b/cadastro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mprj-my.sharepoint.com/personal/pedro_naia_mprj_mp_br/Documents/Documentos/Projeto_AutoComprasNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="11_01FAF3B6D3748A9C493BDD5BE9638AD5C962BAFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1C4E86FC-17E5-4036-8DFB-16BD73736863}"/>
+  <xr:revisionPtr revIDLastSave="16" documentId="11_01FAF3B6D3748A9C493BDD5BE9638AD5C962BAFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B34C7C9-4058-40D5-B45F-154B19834935}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -526,7 +526,13 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="cadastro" displayName="cadastro" ref="A1:AA19" totalsRowShown="0">
-  <autoFilter ref="A1:AA19" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <autoFilter ref="A1:AA19" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="20.22.0001.0056698.2026-15"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AA16">
     <sortCondition ref="A2:A16"/>
     <sortCondition ref="C2:C16"/>
@@ -1588,7 +1594,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -1736,7 +1742,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -1810,7 +1816,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -1884,7 +1890,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -1958,7 +1964,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -2032,7 +2038,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>119</v>
       </c>
@@ -2106,7 +2112,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>125</v>
       </c>
@@ -2180,7 +2186,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>133</v>
       </c>
@@ -2254,7 +2260,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>139</v>
       </c>

--- a/cadastro.xlsx
+++ b/cadastro.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mprj-my.sharepoint.com/personal/pedro_naia_mprj_mp_br/Documents/Documentos/Projeto_AutoComprasNet/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="16" documentId="11_01FAF3B6D3748A9C493BDD5BE9638AD5C962BAFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9B34C7C9-4058-40D5-B45F-154B19834935}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="11_01FAF3B6D3748A9C493BDD5BE9638AD5C962BAFE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BF43385F-140A-4BD6-BB06-E4FFA2853520}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="333" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="343" uniqueCount="148">
   <si>
     <t>PROCESSO</t>
   </si>
@@ -458,6 +458,12 @@
   </si>
   <si>
     <t>DATA_INICIO</t>
+  </si>
+  <si>
+    <t>processoLink</t>
+  </si>
+  <si>
+    <t>https://sei.mprj.mp.br/sei/controlador.php?acao=procedimento_trabalhar&amp;id_procedimento=6409929</t>
   </si>
 </sst>
 </file>
@@ -525,8 +531,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="cadastro" displayName="cadastro" ref="A1:AA19" totalsRowShown="0">
-  <autoFilter ref="A1:AA19" xr:uid="{00000000-0009-0000-0100-000001000000}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="cadastro" displayName="cadastro" ref="A1:AB19" totalsRowShown="0">
+  <autoFilter ref="A1:AB19" xr:uid="{00000000-0009-0000-0100-000001000000}">
     <filterColumn colId="0">
       <filters>
         <filter val="20.22.0001.0056698.2026-15"/>
@@ -537,7 +543,7 @@
     <sortCondition ref="A2:A16"/>
     <sortCondition ref="C2:C16"/>
   </sortState>
-  <tableColumns count="27">
+  <tableColumns count="28">
     <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="PROCESSO"/>
     <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="VALOR"/>
     <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="CNPJ_CPF_FORNECEDOR"/>
@@ -565,6 +571,7 @@
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="STATUS"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="PERC_CONCLUSAO"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="DISPENSA_SIGFIS"/>
+    <tableColumn id="28" xr3:uid="{5DF8E167-7FD8-4F31-8EA2-5F8C99527959}" name="processoLink"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -887,7 +894,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AB19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="25.5703125" bestFit="1" customWidth="1"/>
@@ -917,9 +924,10 @@
     <col min="25" max="25" width="39" customWidth="1"/>
     <col min="26" max="26" width="21.140625" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1001,8 +1009,11 @@
       <c r="AA1" t="s">
         <v>25</v>
       </c>
+      <c r="AB1" t="s">
+        <v>146</v>
+      </c>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>26</v>
       </c>
@@ -1075,8 +1086,11 @@
       <c r="AA2" t="s">
         <v>42</v>
       </c>
+      <c r="AB2" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>26</v>
       </c>
@@ -1149,8 +1163,11 @@
       <c r="AA3" t="s">
         <v>46</v>
       </c>
+      <c r="AB3" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>26</v>
       </c>
@@ -1223,8 +1240,11 @@
       <c r="AA4" t="s">
         <v>50</v>
       </c>
+      <c r="AB4" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>26</v>
       </c>
@@ -1297,8 +1317,11 @@
       <c r="AA5" t="s">
         <v>54</v>
       </c>
+      <c r="AB5" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>26</v>
       </c>
@@ -1371,8 +1394,11 @@
       <c r="AA6" t="s">
         <v>58</v>
       </c>
+      <c r="AB6" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>26</v>
       </c>
@@ -1445,8 +1471,11 @@
       <c r="AA7" t="s">
         <v>62</v>
       </c>
+      <c r="AB7" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -1519,8 +1548,11 @@
       <c r="AA8" t="s">
         <v>66</v>
       </c>
+      <c r="AB8" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>26</v>
       </c>
@@ -1593,8 +1625,11 @@
       <c r="AA9" t="s">
         <v>70</v>
       </c>
+      <c r="AB9" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="10" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>71</v>
       </c>
@@ -1668,7 +1703,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>26</v>
       </c>
@@ -1741,8 +1776,11 @@
       <c r="AA11" t="s">
         <v>86</v>
       </c>
+      <c r="AB11" t="s">
+        <v>147</v>
+      </c>
     </row>
-    <row r="12" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>87</v>
       </c>
@@ -1816,7 +1854,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="13" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>87</v>
       </c>
@@ -1890,7 +1928,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="14" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>102</v>
       </c>
@@ -1964,7 +2002,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="15" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>113</v>
       </c>
@@ -2038,7 +2076,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="16" spans="1:27" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>119</v>
       </c>
